--- a/SQExcel.Portal/src/content/docs/ja/docs/images/foreign-key-order/foreign-key-order.xlsx
+++ b/SQExcel.Portal/src/content/docs/ja/docs/images/foreign-key-order/foreign-key-order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_MS\East\SQL2Excel\v100\SQL2Excel\SQL2Excel.Help\src\content\docs\ja\images\foreign-key-order\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_GitEms\sqexcel\SQExcel.Portal\src\content\docs\ja\docs\images\foreign-key-order\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A0A267A-7A3D-4EBA-949E-3225919DB47F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECF7D659-A04A-43A5-B763-BF3DC17D0288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="940" yWindow="1330" windowWidth="20820" windowHeight="13610" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="19200" windowHeight="11900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FOREIGN_KEY_INPUT" sheetId="4" r:id="rId1"/>
@@ -1238,94 +1238,6 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>199</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>182880</xdr:colOff>
-      <xdr:row>234</xdr:row>
-      <xdr:rowOff>188258</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="図 14">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{096A9EFF-BCBB-276B-18BE-F879C5D95CF8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="234950" y="45720001"/>
-          <a:ext cx="8641080" cy="8189257"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>46</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>108686</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D612BCE-BFB8-2F9A-FE4A-8D23D600BCC5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="234950" y="1371600"/>
-          <a:ext cx="10801350" cy="6509486"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -1349,7 +1261,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1393,7 +1305,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1437,7 +1349,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1481,7 +1393,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1500,72 +1412,170 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>128039</xdr:colOff>
-      <xdr:row>216</xdr:row>
-      <xdr:rowOff>186558</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>199</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>39454</xdr:colOff>
-      <xdr:row>217</xdr:row>
-      <xdr:rowOff>209282</xdr:rowOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>182880</xdr:colOff>
+      <xdr:row>234</xdr:row>
+      <xdr:rowOff>188258</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="正方形/長方形 11">
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="40" name="グループ化 39">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECCD1D51-C985-422F-93FA-B50C37FBD53B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54E88D11-516D-3F56-3992-882536D8D955}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4528215" y="50441205"/>
-          <a:ext cx="2690474" cy="254312"/>
+          <a:off x="231588" y="46086060"/>
+          <a:ext cx="8520057" cy="8293845"/>
+          <a:chOff x="234950" y="45491401"/>
+          <a:chExt cx="8641080" cy="8189257"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="19050">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-          <a:prstTxWarp prst="textNoShape">
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="39" name="グループ化 38">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8D53BB4-8A6E-B628-A620-D5057F23B96C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="234950" y="45491401"/>
+            <a:ext cx="8641080" cy="8189257"/>
+            <a:chOff x="234950" y="45491401"/>
+            <a:chExt cx="8641080" cy="8189257"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="15" name="図 14">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{096A9EFF-BCBB-276B-18BE-F879C5D95CF8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="234950" y="45491401"/>
+              <a:ext cx="8641080" cy="8189257"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="31" name="図 30">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1944923-18CA-4476-8EE7-A1F7F0C3CC11}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="271780" y="45544362"/>
+              <a:ext cx="251903" cy="225837"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="12" name="正方形/長方形 11">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECCD1D51-C985-422F-93FA-B50C37FBD53B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4592089" y="49564158"/>
+            <a:ext cx="2730815" cy="251324"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
             <a:avLst/>
-          </a:prstTxWarp>
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
@@ -1695,107 +1705,161 @@
       <xdr:row>344</xdr:row>
       <xdr:rowOff>188258</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="図 20">
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="38" name="グループ化 37">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2C0B7CD-2A98-A406-EC38-7CC48151A767}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{631F0674-FB11-2417-E14D-2F5C2AF07B53}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="234950" y="71094601"/>
-          <a:ext cx="8641080" cy="8189257"/>
+          <a:off x="231588" y="71560766"/>
+          <a:ext cx="8520057" cy="8293845"/>
+          <a:chOff x="234950" y="70637401"/>
+          <a:chExt cx="8641080" cy="8189257"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>112060</xdr:colOff>
-      <xdr:row>326</xdr:row>
-      <xdr:rowOff>201708</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>224119</xdr:colOff>
-      <xdr:row>327</xdr:row>
-      <xdr:rowOff>216648</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="22" name="正方形/長方形 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE485B5C-C3E8-4D96-BD1D-230AF29F83AC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4512236" y="76162649"/>
-          <a:ext cx="2891118" cy="246528"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="19050">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-          <a:prstTxWarp prst="textNoShape">
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="37" name="グループ化 36">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17302DF9-624C-EE8B-B160-25F1C3762686}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="234950" y="70637401"/>
+            <a:ext cx="8641080" cy="8189257"/>
+            <a:chOff x="234950" y="70637401"/>
+            <a:chExt cx="8641080" cy="8189257"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="21" name="図 20">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2C0B7CD-2A98-A406-EC38-7CC48151A767}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="234950" y="70637401"/>
+              <a:ext cx="8641080" cy="8189257"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="35" name="図 34">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F32F390B-8C67-4144-B381-07682F624B48}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="279146" y="70682795"/>
+              <a:ext cx="251903" cy="225837"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="22" name="正方形/長方形 21">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE485B5C-C3E8-4D96-BD1D-230AF29F83AC}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr>
+            <a:spLocks noChangeAspect="1"/>
+          </xdr:cNvSpPr>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4576110" y="74725308"/>
+            <a:ext cx="2931459" cy="243540"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
             <a:avLst/>
-          </a:prstTxWarp>
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
@@ -1890,21 +1954,21 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>103</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>46</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>131</xdr:row>
-      <xdr:rowOff>75831</xdr:rowOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>108686</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="10" name="グループ化 9">
+        <xdr:cNvPr id="17" name="グループ化 16">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{512B2818-DAF6-CDE8-FB0D-87CE5AD57FF5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37F93295-43CA-44DB-162B-C79D27A18637}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1912,18 +1976,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="231588" y="23853588"/>
-          <a:ext cx="10650071" cy="6560302"/>
-          <a:chOff x="234950" y="23545800"/>
-          <a:chExt cx="10801350" cy="6476631"/>
+          <a:off x="231588" y="1389529"/>
+          <a:ext cx="10650071" cy="6593157"/>
+          <a:chOff x="234950" y="1371600"/>
+          <a:chExt cx="10801366" cy="6509488"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="9" name="図 8">
+          <xdr:cNvPr id="3" name="図 2">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB973988-B5FB-7DAD-58D5-A2AD0EE6B15C}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D612BCE-BFB8-2F9A-FE4A-8D23D600BCC5}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1939,8 +2003,8 @@
         </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="234950" y="23545800"/>
-            <a:ext cx="10801350" cy="6476631"/>
+            <a:off x="234950" y="1371600"/>
+            <a:ext cx="10801366" cy="6509488"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -1949,10 +2013,10 @@
       </xdr:pic>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="5" name="図 4">
+          <xdr:cNvPr id="14" name="図 13">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C1ECECE-513A-C61F-E1EC-8FB72CC57FB4}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51D13C76-F31B-4D2C-8D14-319B6DEF2697}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1961,15 +2025,157 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
         </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="7666566" y="24946350"/>
-            <a:ext cx="655230" cy="1821745"/>
+            <a:off x="249891" y="1416423"/>
+            <a:ext cx="252071" cy="225938"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>131</xdr:row>
+      <xdr:rowOff>75831</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="25" name="グループ化 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{554B2F92-4DE3-40B6-527B-6867D330A5E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="231588" y="23853588"/>
+          <a:ext cx="10650071" cy="6560302"/>
+          <a:chOff x="234950" y="23545800"/>
+          <a:chExt cx="10801350" cy="6476631"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="10" name="グループ化 9">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{512B2818-DAF6-CDE8-FB0D-87CE5AD57FF5}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="234950" y="23545800"/>
+            <a:ext cx="10801350" cy="6476631"/>
+            <a:chOff x="234950" y="23545800"/>
+            <a:chExt cx="10801350" cy="6476631"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="9" name="図 8">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB973988-B5FB-7DAD-58D5-A2AD0EE6B15C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="234950" y="23545800"/>
+              <a:ext cx="10801350" cy="6476631"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="5" name="図 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C1ECECE-513A-C61F-E1EC-8FB72CC57FB4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7666566" y="24946350"/>
+              <a:ext cx="655230" cy="1821745"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="18" name="図 17">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05D7CEEC-C198-4982-8BC7-F5950ACEF6C5}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="242421" y="23560742"/>
+            <a:ext cx="252071" cy="225939"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -1994,10 +2200,10 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="13" name="グループ化 12">
+        <xdr:cNvPr id="34" name="グループ化 33">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{665403A5-9C4D-1003-740C-9F2D015D003F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B2B0EC4-1E01-E621-6091-A9DE19AC15C1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2011,12 +2217,90 @@
           <a:chExt cx="10801350" cy="6509487"/>
         </a:xfrm>
       </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="13" name="グループ化 12">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{665403A5-9C4D-1003-740C-9F2D015D003F}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="234950" y="54864001"/>
+            <a:ext cx="10801350" cy="6509487"/>
+            <a:chOff x="234950" y="54864001"/>
+            <a:chExt cx="10801350" cy="6509487"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="16" name="図 15">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F260AB83-E5B1-C31B-1CD4-7CF51A58835E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="234950" y="54864001"/>
+              <a:ext cx="10801350" cy="6509487"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="11" name="図 10">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07BEF4B2-6C25-421D-A6BF-3C9F3357D7BA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7648576" y="56254650"/>
+              <a:ext cx="654815" cy="1821854"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="16" name="図 15">
+          <xdr:cNvPr id="33" name="図 32">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F260AB83-E5B1-C31B-1CD4-7CF51A58835E}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFA1589B-AE8D-4CE4-9F79-790CFB91634E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2025,44 +2309,15 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
         </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="234950" y="54864001"/>
-            <a:ext cx="10801350" cy="6509487"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="11" name="図 10">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07BEF4B2-6C25-421D-A6BF-3C9F3357D7BA}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="7648576" y="56254650"/>
-            <a:ext cx="654815" cy="1821854"/>
+            <a:off x="249892" y="54886413"/>
+            <a:ext cx="252071" cy="225938"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
